--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2364-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2364-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CBB9DED-444A-4B6E-A8EE-6A8CC52AADB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60FAADFA-0E2A-48FB-9E02-011124AAA47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{91921ACE-71CB-4F4A-A152-ACC854590BF0}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A0E02F9C-59AC-402D-8C5F-4D16DA7D0994}"/>
   </bookViews>
   <sheets>
     <sheet name="2364-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1403,18 +1403,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D8ED1D-D4BA-41BD-8BF1-8F088F430D38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759B1C6F-D28F-4950-9832-F2672F3C359D}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1442,7 +1442,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1472,7 +1472,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1568,7 +1568,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>2024</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>2023</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>2021</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>2019</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>2017</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>2015</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>2013</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="35">
         <v>2011</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="35">
         <v>2009</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35">
         <v>2007</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2006</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="35">
         <v>2005</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2004</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="35">
         <v>2003</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2002</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="35">
         <v>2001</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>1999</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="35">
         <v>1997</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>1996</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
         <v>1995</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>1994</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="35">
         <v>1993</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
         <v>25</v>
       </c>
